--- a/simulations/AON_84/mass_flow_data_AON_84.xlsx
+++ b/simulations/AON_84/mass_flow_data_AON_84.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\simulations\AON_84\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDB3E7D-58BC-4E4D-8B79-9EDFDADADD8F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D7BD7F-785F-4ED4-B5EA-FD96BA88F729}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Material streams" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
   <si>
     <t>Component</t>
   </si>
@@ -224,9 +224,6 @@
     <t>Stream name</t>
   </si>
   <si>
-    <t>HP steam generation</t>
-  </si>
-  <si>
     <t>Data used for calculating the mass flow rate taken from Aspen energy analyzer</t>
   </si>
   <si>
@@ -302,6 +299,9 @@
   </si>
   <si>
     <t>Oxygen</t>
+  </si>
+  <si>
+    <t>Refrigeration to -175 C</t>
   </si>
 </sst>
 </file>
@@ -752,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -790,20 +790,20 @@
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="4">
-        <v>65709.215811999995</v>
+        <v>68241.920832000003</v>
       </c>
       <c r="E4" s="5">
-        <f>D4/$D$10</f>
-        <v>1.7522503801127427</v>
+        <f t="shared" ref="E4:E12" si="0">D4/$D$12</f>
+        <v>1.8198065410276767</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
@@ -817,11 +817,11 @@
         <v>23</v>
       </c>
       <c r="D5" s="4">
-        <v>36320.042282509799</v>
+        <v>36320.042289322097</v>
       </c>
       <c r="E5" s="5">
-        <f>D5/$D$10</f>
-        <v>0.96853701735421172</v>
+        <f t="shared" si="0"/>
+        <v>0.96854616228089385</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -838,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="5">
-        <f>D6/$D$10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -853,77 +853,73 @@
         <v>24</v>
       </c>
       <c r="D7" s="4">
-        <v>59623.526384597099</v>
+        <v>59623.513232212397</v>
       </c>
       <c r="E7" s="5">
-        <f>D7/$D$10</f>
-        <v>1.5899649003571406</v>
+        <f t="shared" si="0"/>
+        <v>1.5899795617732817</v>
       </c>
       <c r="F7" s="18">
-        <f>E7-E6</f>
-        <v>1.5899649003571406</v>
-      </c>
-      <c r="G7" s="1">
-        <f>F7/1000</f>
-        <v>1.5899649003571405E-3</v>
+        <f>E7/1000</f>
+        <v>1.5899795617732818E-3</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="4">
-        <v>4586.5058866173204</v>
+        <v>4586.4960930452999</v>
       </c>
       <c r="E8" s="5">
-        <f>D8/$D$10</f>
-        <v>0.12230714647711328</v>
+        <f t="shared" si="0"/>
+        <v>0.12230804011319479</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D9" s="20">
-        <v>319.44997704349601</v>
+        <v>319.37403200443799</v>
       </c>
       <c r="E9" s="5">
-        <f>D9/$D$10</f>
-        <v>8.5186885398691459E-3</v>
+        <f t="shared" si="0"/>
+        <v>8.5167437462212083E-3</v>
       </c>
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="4">
-        <v>37499.901017440301</v>
+        <v>24</v>
+      </c>
+      <c r="D10" s="20">
+        <v>0.569063764227974</v>
       </c>
       <c r="E10" s="5">
-        <f>D10/$D$10</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>1.5175217048085957E-5</v>
       </c>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
@@ -931,12 +927,44 @@
       <c r="K10" s="17"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="20">
+        <v>2532.4637465507399</v>
+      </c>
+      <c r="E11" s="5">
+        <f t="shared" si="0"/>
+        <v>6.7533182458830068E-2</v>
+      </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <v>37499.546953745201</v>
+      </c>
+      <c r="E12" s="5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
       <c r="J12" s="17"/>
@@ -1475,6 +1503,18 @@
       <c r="I101" s="17"/>
       <c r="J101" s="17"/>
       <c r="K101" s="17"/>
+    </row>
+    <row r="102" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H102" s="17"/>
+      <c r="I102" s="17"/>
+      <c r="J102" s="17"/>
+      <c r="K102" s="17"/>
+    </row>
+    <row r="103" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H103" s="17"/>
+      <c r="I103" s="17"/>
+      <c r="J103" s="17"/>
+      <c r="K103" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1506,7 +1546,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1517,28 +1557,28 @@
         <v>7</v>
       </c>
       <c r="C3" s="4">
-        <v>1791.396</v>
+        <v>1791.4096500000001</v>
       </c>
       <c r="D3" s="5">
-        <f>C3/'Material streams'!$D$10</f>
-        <v>4.7770686092394349E-2</v>
+        <f>C3/'Material streams'!$D$12</f>
+        <v>4.7771501138658058E-2</v>
       </c>
       <c r="E3" s="15"/>
       <c r="F3" s="15"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="4">
-        <v>676.195155</v>
+        <v>676.20022900000004</v>
       </c>
       <c r="D4" s="5">
-        <f>C4/'Material streams'!$D$10</f>
-        <v>1.8031918395878376E-2</v>
+        <f>C4/'Material streams'!$D$12</f>
+        <v>1.8032223958174134E-2</v>
       </c>
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
@@ -1550,11 +1590,11 @@
       </c>
       <c r="C5" s="13">
         <f>SUM(C3:C4)</f>
-        <v>2467.5911550000001</v>
+        <v>2467.6098790000001</v>
       </c>
       <c r="D5" s="16">
         <f>SUM(D3:D4)</f>
-        <v>6.5802604488272728E-2</v>
+        <v>6.5803725096832189E-2</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
@@ -1573,7 +1613,7 @@
     <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
@@ -1588,26 +1628,30 @@
         <v>11</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B2" s="4">
-        <v>549591996.73723197</v>
+        <v>21479811.999867301</v>
       </c>
       <c r="C2" s="4">
         <f>B2/B8/E8</f>
-        <v>322700.95516248723</v>
+        <v>16017756.897738481</v>
       </c>
       <c r="D2" s="4">
-        <f>C2/'Material streams'!$D$10</f>
-        <v>8.6053815185380564</v>
+        <f>C2/'Material streams'!$D$12</f>
+        <v>427.14534438232022</v>
+      </c>
+      <c r="E2" s="19">
+        <f>B2/1000/'Material streams'!$D$12</f>
+        <v>0.57280190681669141</v>
       </c>
       <c r="H2" s="10"/>
     </row>
@@ -1616,21 +1660,24 @@
         <v>17</v>
       </c>
       <c r="B3" s="4">
-        <v>198825004.077851</v>
+        <v>729433625.35782301</v>
       </c>
       <c r="C3" s="4">
         <f>B3/B9/E9</f>
-        <v>9506335.361121254</v>
+        <v>34876099.706326708</v>
       </c>
       <c r="D3" s="4">
-        <f>C3/'Material streams'!$D$10</f>
-        <v>253.50294542644488</v>
-      </c>
-      <c r="E3" s="19"/>
+        <f>C3/'Material streams'!$D$12</f>
+        <v>930.04056153919794</v>
+      </c>
+      <c r="E3" s="19">
+        <f>B3/1000/'Material streams'!$D$12</f>
+        <v>19.451798344592323</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" x14ac:dyDescent="0.35">
@@ -1652,16 +1699,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3">
-        <v>1703.1</v>
+        <v>1.341</v>
       </c>
       <c r="C8" s="3">
-        <v>249</v>
+        <v>174</v>
       </c>
       <c r="D8" s="3">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="E8" s="3">
         <f>D8-C8</f>
